--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_nuble.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_nuble.xlsx
@@ -391,7 +391,7 @@
         <v>133.3086030480077</v>
       </c>
       <c r="C2">
-        <v>16.27049592596318</v>
+        <v>16.27049592596319</v>
       </c>
       <c r="D2">
         <v>62.0395332461523</v>
@@ -410,10 +410,10 @@
         <v>151.3270142180095</v>
       </c>
       <c r="C3">
-        <v>16.44134491759847</v>
+        <v>16.44134491759848</v>
       </c>
       <c r="D3">
-        <v>58.67845872131531</v>
+        <v>58.67845872131532</v>
       </c>
       <c r="E3">
         <v>24.88019636108622</v>
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>154.016620498615</v>
+        <v>154.0166204986149</v>
       </c>
       <c r="C6">
         <v>16.10528663841178</v>
@@ -473,7 +473,7 @@
         <v>59.08989515949141</v>
       </c>
       <c r="E6">
-        <v>24.80481820209681</v>
+        <v>24.8048182020968</v>
       </c>
     </row>
     <row r="7">
@@ -492,7 +492,7 @@
         <v>60.23759131562777</v>
       </c>
       <c r="E7">
-        <v>25.17921758721923</v>
+        <v>25.17921758721922</v>
       </c>
     </row>
     <row r="8">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="B8">
-        <v>192.3339540657976</v>
+        <v>192.3339540657977</v>
       </c>
       <c r="C8">
         <v>14.62285558682037</v>
       </c>
       <c r="D8">
-        <v>57.25242806571662</v>
+        <v>57.25242806571661</v>
       </c>
       <c r="E8">
         <v>28.12471634746301</v>
@@ -540,13 +540,13 @@
         </is>
       </c>
       <c r="B10">
-        <v>158.2785602503912</v>
+        <v>158.2785602503913</v>
       </c>
       <c r="C10">
         <v>15.82466567607727</v>
       </c>
       <c r="D10">
-        <v>59.1282813273898</v>
+        <v>59.12828132738979</v>
       </c>
       <c r="E10">
         <v>25.04705299653294</v>
@@ -603,7 +603,7 @@
         <v>15.10775626299092</v>
       </c>
       <c r="D13">
-        <v>58.59315173394596</v>
+        <v>58.59315173394595</v>
       </c>
       <c r="E13">
         <v>26.29909200306312</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>228.2352941176471</v>
+        <v>228.235294117647</v>
       </c>
       <c r="C15">
         <v>13.01463082681184</v>
@@ -644,7 +644,7 @@
         <v>57.28138822728819</v>
       </c>
       <c r="E15">
-        <v>29.70398094589997</v>
+        <v>29.70398094589996</v>
       </c>
     </row>
     <row r="16">
@@ -682,7 +682,7 @@
         <v>55.64927422518635</v>
       </c>
       <c r="E17">
-        <v>28.03060023538643</v>
+        <v>28.03060023538642</v>
       </c>
     </row>
     <row r="18">
@@ -698,7 +698,7 @@
         <v>15.97910164201384</v>
       </c>
       <c r="D18">
-        <v>59.48907585832541</v>
+        <v>59.48907585832542</v>
       </c>
       <c r="E18">
         <v>24.53182249966074</v>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>126.1348271199536</v>
+        <v>126.1348271199537</v>
       </c>
       <c r="C19">
         <v>17.03689077566064</v>
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="B20">
-        <v>71.60243407707911</v>
+        <v>71.6024340770791</v>
       </c>
       <c r="C20">
         <v>21.282106626376</v>
       </c>
       <c r="D20">
-        <v>63.47938700625944</v>
+        <v>63.47938700625945</v>
       </c>
       <c r="E20">
         <v>15.23850636736456</v>
@@ -755,7 +755,7 @@
         <v>15.14223194748359</v>
       </c>
       <c r="D21">
-        <v>62.23194748358862</v>
+        <v>62.23194748358863</v>
       </c>
       <c r="E21">
         <v>22.62582056892779</v>
